--- a/internal_doc/05.测试设计/OM/集合/OM-集合-测试设计.xlsx
+++ b/internal_doc/05.测试设计/OM/集合/OM-集合-测试设计.xlsx
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="94">
   <si>
     <t>特性</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -118,98 +118,328 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>嵌套的一些参数选项多次切换后参数仍能正确显示</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建‘水平散列分区’集合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1)CS所在域没有关联group，创建集合时指定分区组为Auto
+2）CS所在域关联了多个group，创建集合时指定分区组为Auto</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单个分区键且升序，关闭索引，创建‘水平范围分区’集合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多个分区键包括升序和降序，开启索引，创建‘水平范围分区’集合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>集合名合法参数校验</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>集合名非法参数校验</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>副本数合法参数校验</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>副本数非法参数校验</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>集合空间默认值和下拉列表检查</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）默认值：关
+2）下拉列表选项:开、关</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）默认值：默认显示列表中第一个集合空间
+2）下拉列表选项跟数据库实际存在的集合空间一致，包括集合空间名和展示的集合空间个数</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>分区索引默认值和下拉列表检查</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）默认值：开
+2）下拉列表选项:开、关</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）默认值、-1、0、7
+2）等于实际副本数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）非数字
+2）大于7
+3）参数无效时tips提示正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>其值必须是2的幂。范围在[2^3, 2^20]，即为8~1048576范围内2的幂次方取值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）字符非法
+2）取值范围非法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建‘垂直分区’集合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单个分区键且降序，创建‘垂直分区’集合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多个分区键升序，创建‘垂直分区’集合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多页面并发创建相同集合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重复创建集合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）创建成功，该集合空间下该集合信息展示正确，包括集合名、分区类型、主集合、Lob数、记录数、索引数
+2）集合属性、分区属性数据正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>页面检查</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除集合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>页面检查</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>挂载集合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多字段分区，挂载集合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已选择的集合在后台已被删除，继续删除</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已选择的子分区集合在后台已被删除，继续挂载</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分区键重复，创建集合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）字段名重复
+2）左区间重复（值重复/被包含在已存在分区范围内）
+3）右区间重复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>字段名非法参数校验</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>左边界/右边界合法参数校验</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>左边界/右边界非法参数校验</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）字段名为分区键字段以外的字段
+2）字符非法，如$
+3）参数无效时tips提示正确</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1)$minKey/$maxKey、数值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>去挂载集合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>没有去挂载的接口提供给OM，暂未实现</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>其他按钮测试（最大化/最小化窗口弹出框、关闭弹出框按钮）</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）字段名为分区键字段
+2）tips提示正确</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）字符非法
+2）长度非法
+3）参数无效时tips提示正确</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）默认值：升序
+2）下拉选项：升序、降序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试项</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试子项</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>功能测试
+表单测试：文本框校验、按钮功能、tip信息、提交信息正确性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>标题栏文本测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>标题栏文本测试</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>集合空间为空，创建集合</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>1）字符合法，包括有效字符和有效取值
 2）长度合法
 3）tips提示正确</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>1）默认值正确
-2）下拉列表选项正确，如：分区组跟实际集群分区组一致</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>嵌套的一些参数选项多次切换后参数仍能正确显示</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建‘水平散列分区’集合</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1)CS所在域没有关联group，创建集合时指定分区组为Auto
-2）CS所在域关联了多个group，创建集合时指定分区组为Auto</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>单个分区键且升序，关闭索引，创建‘水平范围分区’集合</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>多个分区键包括升序和降序，开启索引，创建‘水平范围分区’集合</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>集合名合法参数校验</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>集合名非法参数校验</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>副本数合法参数校验</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>副本数非法参数校验</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>集合空间默认值和下拉列表检查</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1）默认值：关
-2）下拉列表选项:开、关</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>1）默认值：默认显示列表中第一个集合空间
-2）下拉列表选项跟数据库实际存在的集合空间一致，包括集合空间名和展示的集合空间个数</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>分区索引默认值和下拉列表检查</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1）默认值：开
-2）下拉列表选项:开、关</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>1）默认值、-1、0、7
-2）等于实际副本数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1）非数字
-2）大于7
-3）参数无效时tips提示正确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>其值必须是2的幂。范围在[2^3, 2^20]，即为8~1048576范围内2的幂次方取值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1）字符非法
-2）取值范围非法</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建‘垂直分区’集合</t>
+    <t>数据压缩默认值和下拉列表检查</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分区组默认值和下拉列表检查</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）默认值：Auto
+2）下拉列表选项:Auto、实际存在的group（包括组名和实际存在的组的个数）</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建集合时添加多个分区键，点击‘删除’其中一个分区键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单个分区键且升序，创建‘水平散列分区’集合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多个分区键降序，创建‘水平散列分区’集合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分区数合法参数校验</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分区数非法参数校验</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动切分默认值和下拉列表检查</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>输入有效参数后“取消”创建</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除已存在集合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择集合后‘取消’删除</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>单字段分区，挂载集合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分区范围重复，挂载集合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已选择的主分区集合在后台已被删除，继续挂载</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>挂载集合时分区范围只有一个，删除该分区范围</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>挂载集合时已添加多个分区范围，删除其中一个分区范围</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>字段名合法参数校验</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>输入有效参数后“取消”挂载</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>浏览器兼容性测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>国际化测试-中英文</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不开数据压缩并指定分区组为Auto，创建普通集合</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>开启数据压缩并指定分区组组名，创建普通集合</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>‘普通’集合参数默认值：
+  集合空间：
+  集合名：
+  数据压缩：关（默认）、开
+  分区组：Auto/groupName（默认Auto）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -224,6 +454,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>分区键字段名为空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分区键默认值和下拉列表检查</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>‘水平散列分区’集合参数默认值：
   集合空间：
   集合名：
@@ -235,260 +473,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>单个分区键且降序，创建‘垂直分区’集合</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>多个分区键升序，创建‘垂直分区’集合</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>多页面并发创建相同集合</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>重复创建集合</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1）创建成功，该集合空间下该集合信息展示正确，包括集合名、分区类型、主集合、Lob数、记录数、索引数
-2）集合属性、分区属性数据正确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>页面检查</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>删除集合</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>页面检查</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>挂载集合</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>多字段分区，挂载集合</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>已选择的集合在后台已被删除，继续删除</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>已选择的子分区集合在后台已被删除，继续挂载</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>分区键重复，创建集合</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1）字段名重复
-2）左区间重复（值重复/被包含在已存在分区范围内）
-3）右区间重复</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>字段名非法参数校验</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>左边界/右边界合法参数校验</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>左边界/右边界非法参数校验</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1）字段名为分区键字段以外的字段
-2）字符非法，如$
-3）参数无效时tips提示正确</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>1)$minKey/$maxKey、数值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>去挂载集合</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>没有去挂载的接口提供给OM，暂未实现</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>其他按钮测试（最大化/最小化窗口弹出框、关闭弹出框按钮）</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>1）字段名为分区键字段
-2）tips提示正确</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>分区键字段名合法参数校验</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>分区键字段名非法参数校验</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1）字符非法
-2）长度非法
-3）参数无效时tips提示正确</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>1）默认值：升序
-2）下拉选项：升序、降序</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>分区键排序下拉列表合法参数校验</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试项</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试子项</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>功能测试
-表单测试：文本框校验、按钮功能、tip信息、提交信息正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>标题栏文本测试</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>标题栏文本测试</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>‘普通’集合参数默认值：
-  集合空间：
-  集合名：
-  数据压缩：关（默认）、开
-  分区组：Auto/groupName（默认Auto）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不开数据压缩并指定分区组为Auto，创建普通集合</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>开启数据压缩并指定分区组组名，创建普通集合</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>集合空间为空，创建集合</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>1）字符合法，包括有效字符和有效取值
-2）长度合法
-3）tips提示正确</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据压缩默认值和下拉列表检查</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>分区组默认值和下拉列表检查</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1）默认值：Auto
-2）下拉列表选项:Auto、实际存在的group（包括组名和实际存在的组的个数）</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建集合时添加多个分区键，点击‘删除’其中一个分区键</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>单个分区键且升序，创建‘水平散列分区’集合</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>多个分区键降序，创建‘水平散列分区’集合</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>分区数合法参数校验</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>分区数非法参数校验</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自动切分默认值和下拉列表检查</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>‘垂直分区’集合参数默认值：
   集合空间：
   集合名：
   分区键：升序（默认）、降序
   副本数：1（默认）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>默认值以及下拉列表选项检查</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>输入有效参数后“取消”创建</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>删除已存在集合</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>选择集合后‘取消’删除</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>单字段分区，挂载集合</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>分区范围重复，挂载集合</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>已选择的主分区集合在后台已被删除，继续挂载</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>挂载集合时分区范围只有一个，删除该分区范围</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>挂载集合时已添加多个分区范围，删除其中一个分区范围</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>字段名合法参数校验</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>输入有效参数后“取消”挂载</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -986,10 +975,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>1</v>
@@ -1003,25 +992,25 @@
         <v>10</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="40.5">
       <c r="A3" s="3"/>
       <c r="C3" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -1031,7 +1020,7 @@
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="8" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -1051,7 +1040,7 @@
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="D6" s="4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
@@ -1061,7 +1050,7 @@
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="6" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
@@ -1071,10 +1060,10 @@
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="D8" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="F8" s="3"/>
     </row>
@@ -1083,10 +1072,10 @@
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="D9" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="F9" s="3"/>
     </row>
@@ -1095,10 +1084,10 @@
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>27</v>
       </c>
       <c r="F10" s="3"/>
     </row>
@@ -1107,10 +1096,10 @@
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="4" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F11" s="3"/>
     </row>
@@ -1119,10 +1108,10 @@
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="4" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="F12" s="3"/>
     </row>
@@ -1132,10 +1121,10 @@
         <v>11</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>35</v>
+        <v>89</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -1145,7 +1134,7 @@
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
@@ -1163,7 +1152,7 @@
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>13</v>
@@ -1177,32 +1166,30 @@
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
     </row>
-    <row r="18" spans="1:6" ht="40.5">
+    <row r="18" spans="1:6">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>14</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="E18" s="3"/>
       <c r="F18" s="3"/>
     </row>
-    <row r="19" spans="1:6" ht="40.5">
+    <row r="19" spans="1:6" ht="27">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="4" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="F19" s="3"/>
     </row>
@@ -1211,71 +1198,71 @@
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
       <c r="D20" s="4" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="F20" s="3"/>
     </row>
-    <row r="21" spans="1:6" ht="27">
+    <row r="21" spans="1:6" ht="40.5">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F21" s="3"/>
     </row>
-    <row r="22" spans="1:6" ht="40.5">
+    <row r="22" spans="1:6" ht="27">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
-      <c r="D22" s="4" t="s">
-        <v>24</v>
+      <c r="D22" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F22" s="3"/>
     </row>
-    <row r="23" spans="1:6" ht="27">
+    <row r="23" spans="1:6" ht="108">
       <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
+      <c r="B23" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>92</v>
+      </c>
       <c r="D23" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>29</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="E23" s="3"/>
       <c r="F23" s="3"/>
     </row>
-    <row r="24" spans="1:6" ht="108">
+    <row r="24" spans="1:6">
       <c r="A24" s="3"/>
-      <c r="B24" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
       <c r="D24" s="3" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" ht="27">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E25" s="3"/>
+        <v>71</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="F25" s="3"/>
     </row>
     <row r="26" spans="1:6" ht="27">
@@ -1283,10 +1270,10 @@
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
       <c r="D26" s="3" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F26" s="3"/>
     </row>
@@ -1295,60 +1282,60 @@
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="E27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F27" s="3"/>
+    </row>
+    <row r="28" spans="1:6" ht="67.5">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F27" s="3"/>
-    </row>
-    <row r="28" spans="1:6" ht="27">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>26</v>
-      </c>
+      <c r="E28" s="3"/>
       <c r="F28" s="3"/>
     </row>
-    <row r="29" spans="1:6" ht="67.5">
+    <row r="29" spans="1:6">
       <c r="A29" s="3"/>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" ht="27">
       <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
+      <c r="B30" s="3" t="s">
+        <v>38</v>
+      </c>
       <c r="C30" s="3"/>
-      <c r="D30" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E30" s="3"/>
+      <c r="D30" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="F30" s="3"/>
     </row>
-    <row r="31" spans="1:6" ht="40.5">
+    <row r="31" spans="1:6">
       <c r="A31" s="3"/>
-      <c r="B31" s="3" t="s">
-        <v>42</v>
-      </c>
+      <c r="B31" s="3"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F31" s="3"/>
     </row>
@@ -1356,11 +1343,11 @@
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
-      <c r="D32" s="5" t="s">
-        <v>4</v>
+      <c r="D32" s="3" t="s">
+        <v>7</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F32" s="3"/>
     </row>
@@ -1369,23 +1356,19 @@
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
       <c r="D33" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>5</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="E33" s="3"/>
       <c r="F33" s="3"/>
     </row>
-    <row r="34" spans="1:6" ht="27">
+    <row r="34" spans="1:6">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
       <c r="D34" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>6</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="E34" s="3"/>
       <c r="F34" s="3"/>
     </row>
     <row r="35" spans="1:6">
@@ -1393,21 +1376,21 @@
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
       <c r="D35" s="3" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C36" s="3"/>
       <c r="D36" s="3" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
@@ -1417,7 +1400,7 @@
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
       <c r="D37" s="3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
@@ -1426,7 +1409,7 @@
       <c r="A38" s="3"/>
       <c r="C38" s="3"/>
       <c r="D38" s="3" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
@@ -1434,7 +1417,7 @@
     <row r="39" spans="1:6" ht="27">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C39" s="3"/>
       <c r="D39" s="3" t="s">
@@ -1448,21 +1431,21 @@
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
       <c r="D40" s="3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C41" s="3"/>
       <c r="D41" s="3" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
@@ -1472,7 +1455,7 @@
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
       <c r="D42" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
@@ -1482,10 +1465,10 @@
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
       <c r="D43" s="3" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F43" s="3"/>
     </row>
@@ -1494,7 +1477,7 @@
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
       <c r="D44" s="3" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
@@ -1504,7 +1487,7 @@
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
       <c r="D45" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
@@ -1514,7 +1497,7 @@
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
       <c r="D46" s="3" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
@@ -1524,7 +1507,7 @@
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
       <c r="D47" s="3" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
@@ -1534,10 +1517,10 @@
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
       <c r="D48" s="3" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F48" s="3"/>
     </row>
@@ -1546,10 +1529,10 @@
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
       <c r="D49" s="3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F49" s="3"/>
     </row>
@@ -1558,10 +1541,10 @@
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
       <c r="D50" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F50" s="3"/>
     </row>
@@ -1570,7 +1553,7 @@
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
       <c r="D51" s="3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
@@ -1580,7 +1563,7 @@
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
       <c r="D52" s="3" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
@@ -1590,7 +1573,7 @@
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
       <c r="D53" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
@@ -1600,7 +1583,7 @@
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
@@ -1608,10 +1591,10 @@
     <row r="55" spans="1:6">
       <c r="A55" s="3"/>
       <c r="B55" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>

--- a/internal_doc/05.测试设计/OM/集合/OM-集合-测试设计.xlsx
+++ b/internal_doc/05.测试设计/OM/集合/OM-集合-测试设计.xlsx
@@ -45,6 +45,32 @@
         </r>
       </text>
     </comment>
+    <comment ref="D38" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+重复，删除该测试点</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -112,12 +138,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1）删除第一个分区键
-2）删除最后一个分区键
-3）删除中间位置分区键</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>嵌套的一些参数选项多次切换后参数仍能正确显示</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -385,10 +405,6 @@
   <si>
     <t>删除已存在集合</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>选择集合后‘取消’删除</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>单字段分区，挂载集合</t>
@@ -479,6 +495,16 @@
   分区键：升序（默认）、降序
   副本数：1（默认）</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）删除第一个分区键
+2）删除最后一个分区键
+3）删除中间位置分区键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择集合后‘取消’删除</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -541,7 +567,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -557,6 +583,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -588,7 +620,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -612,6 +644,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -975,10 +1010,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>1</v>
@@ -992,25 +1027,25 @@
         <v>10</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="40.5">
       <c r="A3" s="3"/>
       <c r="C3" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -1020,7 +1055,7 @@
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -1040,7 +1075,7 @@
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="D6" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
@@ -1050,7 +1085,7 @@
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
@@ -1060,10 +1095,10 @@
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="D8" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F8" s="3"/>
     </row>
@@ -1072,10 +1107,10 @@
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="D9" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F9" s="3"/>
     </row>
@@ -1084,10 +1119,10 @@
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F10" s="3"/>
     </row>
@@ -1096,10 +1131,10 @@
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F11" s="3"/>
     </row>
@@ -1108,10 +1143,10 @@
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="F12" s="3"/>
     </row>
@@ -1121,10 +1156,10 @@
         <v>11</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -1134,7 +1169,7 @@
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
@@ -1152,10 +1187,10 @@
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>12</v>
@@ -1166,7 +1201,7 @@
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
@@ -1176,7 +1211,7 @@
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
@@ -1186,10 +1221,10 @@
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F19" s="3"/>
     </row>
@@ -1198,10 +1233,10 @@
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
       <c r="D20" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F20" s="3"/>
     </row>
@@ -1210,10 +1245,10 @@
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F21" s="3"/>
     </row>
@@ -1222,23 +1257,23 @@
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>27</v>
       </c>
       <c r="F22" s="3"/>
     </row>
     <row r="23" spans="1:6" ht="108">
       <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
@@ -1248,7 +1283,7 @@
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
@@ -1258,10 +1293,10 @@
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F25" s="3"/>
     </row>
@@ -1270,10 +1305,10 @@
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
       <c r="D26" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F26" s="3"/>
     </row>
@@ -1282,23 +1317,23 @@
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F27" s="3"/>
     </row>
     <row r="28" spans="1:6" ht="67.5">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>33</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
@@ -1308,7 +1343,7 @@
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
       <c r="D29" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
@@ -1316,14 +1351,14 @@
     <row r="30" spans="1:6" ht="27">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C30" s="3"/>
       <c r="D30" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F30" s="3"/>
     </row>
@@ -1332,7 +1367,7 @@
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>5</v>
@@ -1356,7 +1391,7 @@
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
       <c r="D33" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
@@ -1366,7 +1401,7 @@
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
       <c r="D34" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
@@ -1376,21 +1411,21 @@
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
       <c r="D35" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C36" s="3"/>
       <c r="D36" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
@@ -1400,7 +1435,7 @@
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
       <c r="D37" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
@@ -1408,8 +1443,8 @@
     <row r="38" spans="1:6">
       <c r="A38" s="3"/>
       <c r="C38" s="3"/>
-      <c r="D38" s="3" t="s">
-        <v>76</v>
+      <c r="D38" s="9" t="s">
+        <v>93</v>
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
@@ -1417,7 +1452,7 @@
     <row r="39" spans="1:6" ht="27">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C39" s="3"/>
       <c r="D39" s="3" t="s">
@@ -1431,21 +1466,21 @@
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
       <c r="D40" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C41" s="3"/>
       <c r="D41" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
@@ -1455,7 +1490,7 @@
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
       <c r="D42" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
@@ -1465,10 +1500,10 @@
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
       <c r="D43" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F43" s="3"/>
     </row>
@@ -1477,7 +1512,7 @@
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
       <c r="D44" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
@@ -1487,7 +1522,7 @@
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
       <c r="D45" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
@@ -1497,7 +1532,7 @@
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
       <c r="D46" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
@@ -1507,7 +1542,7 @@
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
       <c r="D47" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
@@ -1517,10 +1552,10 @@
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
       <c r="D48" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F48" s="3"/>
     </row>
@@ -1529,10 +1564,10 @@
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
       <c r="D49" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F49" s="3"/>
     </row>
@@ -1541,10 +1576,10 @@
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
       <c r="D50" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F50" s="3"/>
     </row>
@@ -1553,7 +1588,7 @@
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
       <c r="D51" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
@@ -1563,7 +1598,7 @@
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
       <c r="D52" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
@@ -1573,7 +1608,7 @@
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
       <c r="D53" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
@@ -1583,7 +1618,7 @@
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
@@ -1591,10 +1626,10 @@
     <row r="55" spans="1:6">
       <c r="A55" s="3"/>
       <c r="B55" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C55" s="7" t="s">
         <v>52</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>53</v>
       </c>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
